--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202605/AllSymbols_P&L_20260505.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202605/AllSymbols_P&L_20260505.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="95">
   <si>
     <t>Symbol</t>
   </si>
@@ -43,6 +43,210 @@
     <t>Market Value USD</t>
   </si>
   <si>
+    <t>6301.T</t>
+  </si>
+  <si>
+    <t>8360.T</t>
+  </si>
+  <si>
+    <t>A17U</t>
+  </si>
+  <si>
+    <t>AVAV</t>
+  </si>
+  <si>
+    <t>AVDV</t>
+  </si>
+  <si>
+    <t>AVEM</t>
+  </si>
+  <si>
+    <t>AVUV</t>
+  </si>
+  <si>
+    <t>BABA</t>
+  </si>
+  <si>
+    <t>BMNR</t>
+  </si>
+  <si>
+    <t>BN4</t>
+  </si>
+  <si>
+    <t>BWXT</t>
+  </si>
+  <si>
+    <t>C6L</t>
+  </si>
+  <si>
+    <t>CEG</t>
+  </si>
+  <si>
+    <t>CLSE</t>
+  </si>
+  <si>
+    <t>CME</t>
+  </si>
+  <si>
+    <t>CNXT</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>COLO</t>
+  </si>
+  <si>
+    <t>CSCO</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>D05</t>
+  </si>
+  <si>
+    <t>DBMF</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>DG</t>
+  </si>
+  <si>
+    <t>EFA</t>
+  </si>
+  <si>
+    <t>EMR</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>EWY</t>
+  </si>
+  <si>
+    <t>EWZ</t>
+  </si>
+  <si>
+    <t>GEV</t>
+  </si>
+  <si>
+    <t>HGER</t>
+  </si>
+  <si>
+    <t>ICE</t>
+  </si>
+  <si>
+    <t>JPM</t>
+  </si>
+  <si>
+    <t>KMLM</t>
+  </si>
+  <si>
+    <t>KORU</t>
+  </si>
+  <si>
+    <t>KRE</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>ME8U</t>
+  </si>
+  <si>
+    <t>MELI</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>NVO</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>PKB</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>QQQ</t>
+  </si>
+  <si>
+    <t>RBLX</t>
+  </si>
+  <si>
+    <t>REMX</t>
+  </si>
+  <si>
+    <t>RTX</t>
+  </si>
+  <si>
+    <t>S68</t>
+  </si>
+  <si>
+    <t>SCHD</t>
+  </si>
+  <si>
+    <t>SCJ</t>
+  </si>
+  <si>
+    <t>SHLD</t>
+  </si>
+  <si>
+    <t>SLI</t>
+  </si>
+  <si>
+    <t>SPXL</t>
+  </si>
+  <si>
+    <t>U11</t>
+  </si>
+  <si>
+    <t>U96</t>
+  </si>
+  <si>
+    <t>USMV</t>
+  </si>
+  <si>
+    <t>VDE</t>
+  </si>
+  <si>
+    <t>VNAM</t>
+  </si>
+  <si>
+    <t>VRT</t>
+  </si>
+  <si>
+    <t>VST</t>
+  </si>
+  <si>
+    <t>VZ</t>
+  </si>
+  <si>
+    <t>XLV</t>
+  </si>
+  <si>
+    <t>Z74</t>
+  </si>
+  <si>
+    <t>EBND</t>
+  </si>
+  <si>
     <t>EMLC</t>
   </si>
   <si>
@@ -52,10 +256,49 @@
     <t>SHYG</t>
   </si>
   <si>
+    <t>AGQ</t>
+  </si>
+  <si>
+    <t>IAUM</t>
+  </si>
+  <si>
+    <t>URA</t>
+  </si>
+  <si>
+    <t>UTES</t>
+  </si>
+  <si>
+    <t>XLE</t>
+  </si>
+  <si>
+    <t>FXY</t>
+  </si>
+  <si>
+    <t>K71U.DIST</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>JPY</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
     <t>USD</t>
   </si>
   <si>
+    <t>Equity</t>
+  </si>
+  <si>
     <t>Bond</t>
+  </si>
+  <si>
+    <t>Commodity</t>
+  </si>
+  <si>
+    <t>FX</t>
   </si>
 </sst>
 </file>
@@ -413,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -446,90 +689,2813 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>1109</v>
+      </c>
+      <c r="B2">
+        <v>2000</v>
+      </c>
+      <c r="C2">
+        <v>33.12</v>
+      </c>
+      <c r="D2">
+        <v>20.42</v>
+      </c>
+      <c r="E2">
+        <v>66240</v>
+      </c>
+      <c r="F2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2">
+        <v>0.1276</v>
+      </c>
+      <c r="I2">
+        <v>8452.219999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>1258</v>
+      </c>
+      <c r="B3">
+        <v>427000</v>
+      </c>
+      <c r="C3">
+        <v>12.68</v>
+      </c>
+      <c r="D3">
+        <v>-10353</v>
+      </c>
+      <c r="E3">
+        <v>5414360</v>
+      </c>
+      <c r="F3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3">
+        <v>0.1276</v>
+      </c>
+      <c r="I3">
+        <v>690872.34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>1288</v>
+      </c>
+      <c r="B4">
+        <v>6000</v>
+      </c>
+      <c r="C4">
+        <v>5.87</v>
+      </c>
+      <c r="D4">
+        <v>-53.6</v>
+      </c>
+      <c r="E4">
+        <v>35220</v>
+      </c>
+      <c r="F4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4">
+        <v>0.1276</v>
+      </c>
+      <c r="I4">
+        <v>4494.07</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>1398</v>
+      </c>
+      <c r="B5">
+        <v>6000</v>
+      </c>
+      <c r="C5">
+        <v>6.9</v>
+      </c>
+      <c r="D5">
+        <v>-15.31</v>
+      </c>
+      <c r="E5">
+        <v>41400</v>
+      </c>
+      <c r="F5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5">
+        <v>0.1276</v>
+      </c>
+      <c r="I5">
+        <v>5282.64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>1698</v>
+      </c>
+      <c r="B6">
+        <v>2000</v>
+      </c>
+      <c r="C6">
+        <v>35.86</v>
+      </c>
+      <c r="D6">
+        <v>35.73</v>
+      </c>
+      <c r="E6">
+        <v>71720</v>
+      </c>
+      <c r="F6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6">
+        <v>0.1276</v>
+      </c>
+      <c r="I6">
+        <v>9151.469999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>1810</v>
+      </c>
+      <c r="B7">
+        <v>200</v>
+      </c>
+      <c r="C7">
+        <v>30.46</v>
+      </c>
+      <c r="D7">
+        <v>-13.27</v>
+      </c>
+      <c r="E7">
+        <v>6092</v>
+      </c>
+      <c r="F7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7">
+        <v>0.1276</v>
+      </c>
+      <c r="I7">
+        <v>777.34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>2359</v>
+      </c>
+      <c r="B8">
+        <v>300</v>
+      </c>
+      <c r="C8">
+        <v>137.3</v>
+      </c>
+      <c r="D8">
+        <v>-3.83</v>
+      </c>
+      <c r="E8">
+        <v>41190</v>
+      </c>
+      <c r="F8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8">
+        <v>0.1276</v>
+      </c>
+      <c r="I8">
+        <v>5255.84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>2800</v>
+      </c>
+      <c r="B9">
+        <v>2000</v>
+      </c>
+      <c r="C9">
+        <v>26.02</v>
+      </c>
+      <c r="D9">
+        <v>-56.15</v>
+      </c>
+      <c r="E9">
+        <v>52040</v>
+      </c>
+      <c r="F9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9">
+        <v>0.1276</v>
+      </c>
+      <c r="I9">
+        <v>6640.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>2828</v>
+      </c>
+      <c r="B10">
+        <v>600</v>
+      </c>
+      <c r="C10">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="D10">
+        <v>-33.69</v>
+      </c>
+      <c r="E10">
+        <v>53724</v>
+      </c>
+      <c r="F10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10">
+        <v>0.1276</v>
+      </c>
+      <c r="I10">
+        <v>6855.18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>2899</v>
+      </c>
+      <c r="B11">
+        <v>110000</v>
+      </c>
+      <c r="C11">
+        <v>35.5</v>
+      </c>
+      <c r="D11">
+        <v>-4211.13</v>
+      </c>
+      <c r="E11">
+        <v>3905000</v>
+      </c>
+      <c r="F11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11">
+        <v>0.1276</v>
+      </c>
+      <c r="I11">
+        <v>498278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>3067</v>
+      </c>
+      <c r="B12">
+        <v>700</v>
+      </c>
+      <c r="C12">
+        <v>10.33</v>
+      </c>
+      <c r="D12">
+        <v>-11.61</v>
+      </c>
+      <c r="E12">
+        <v>7231</v>
+      </c>
+      <c r="F12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12">
+        <v>0.1276</v>
+      </c>
+      <c r="I12">
+        <v>922.6799999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>3750</v>
+      </c>
+      <c r="B13">
+        <v>4700</v>
+      </c>
+      <c r="C13">
+        <v>655</v>
+      </c>
+      <c r="D13">
+        <v>14094.52</v>
+      </c>
+      <c r="E13">
+        <v>3078500</v>
+      </c>
+      <c r="F13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13">
+        <v>0.1276</v>
+      </c>
+      <c r="I13">
+        <v>392816.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>388</v>
+      </c>
+      <c r="B14">
+        <v>23500</v>
+      </c>
+      <c r="C14">
+        <v>418.2</v>
+      </c>
+      <c r="D14">
+        <v>9596.27</v>
+      </c>
+      <c r="E14">
+        <v>9827700</v>
+      </c>
+      <c r="F14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14">
+        <v>0.1276</v>
+      </c>
+      <c r="I14">
+        <v>1254014.52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>3988</v>
+      </c>
+      <c r="B15">
+        <v>4000</v>
+      </c>
+      <c r="C15">
+        <v>5.05</v>
+      </c>
+      <c r="D15">
+        <v>-20.42</v>
+      </c>
+      <c r="E15">
+        <v>20200</v>
+      </c>
+      <c r="F15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15">
+        <v>0.1276</v>
+      </c>
+      <c r="I15">
+        <v>2577.52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
-        <v>10882</v>
-      </c>
-      <c r="C2">
+      <c r="B16">
+        <v>35300</v>
+      </c>
+      <c r="C16">
+        <v>6514</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>229944200</v>
+      </c>
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16">
+        <v>0.0063</v>
+      </c>
+      <c r="I16">
+        <v>1448648.46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17">
+        <v>700</v>
+      </c>
+      <c r="B17">
+        <v>200</v>
+      </c>
+      <c r="C17">
+        <v>472.2</v>
+      </c>
+      <c r="D17">
+        <v>-20.42</v>
+      </c>
+      <c r="E17">
+        <v>94440</v>
+      </c>
+      <c r="F17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17">
+        <v>0.1276</v>
+      </c>
+      <c r="I17">
+        <v>12050.54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18">
+        <v>762</v>
+      </c>
+      <c r="B18">
+        <v>16000</v>
+      </c>
+      <c r="C18">
+        <v>7.32</v>
+      </c>
+      <c r="D18">
+        <v>-40.84</v>
+      </c>
+      <c r="E18">
+        <v>117120</v>
+      </c>
+      <c r="F18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18">
+        <v>0.1276</v>
+      </c>
+      <c r="I18">
+        <v>14944.51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <v>2100</v>
+      </c>
+      <c r="C19">
+        <v>5390</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>11319000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19">
+        <v>0.0063</v>
+      </c>
+      <c r="I19">
+        <v>71309.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20">
+        <v>857</v>
+      </c>
+      <c r="B20">
+        <v>342000</v>
+      </c>
+      <c r="C20">
+        <v>11.68</v>
+      </c>
+      <c r="D20">
+        <v>-872.85</v>
+      </c>
+      <c r="E20">
+        <v>3994560</v>
+      </c>
+      <c r="F20" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20">
+        <v>0.1276</v>
+      </c>
+      <c r="I20">
+        <v>509705.86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21">
+        <v>883</v>
+      </c>
+      <c r="B21">
+        <v>106000</v>
+      </c>
+      <c r="C21">
+        <v>28.56</v>
+      </c>
+      <c r="D21">
+        <v>-811.6</v>
+      </c>
+      <c r="E21">
+        <v>3027360</v>
+      </c>
+      <c r="F21" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21">
+        <v>0.1276</v>
+      </c>
+      <c r="I21">
+        <v>386291.14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22">
+        <v>9633</v>
+      </c>
+      <c r="B22">
+        <v>1800</v>
+      </c>
+      <c r="C22">
+        <v>45.7</v>
+      </c>
+      <c r="D22">
+        <v>-151.6</v>
+      </c>
+      <c r="E22">
+        <v>82260</v>
+      </c>
+      <c r="F22" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22">
+        <v>0.1276</v>
+      </c>
+      <c r="I22">
+        <v>10496.38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>6000</v>
+      </c>
+      <c r="C23">
+        <v>2.51</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>15060</v>
+      </c>
+      <c r="F23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23">
+        <v>0.784</v>
+      </c>
+      <c r="I23">
+        <v>11807.04</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>166.69</v>
+      </c>
+      <c r="D24">
+        <v>2425.52</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25">
+        <v>18900</v>
+      </c>
+      <c r="C25">
+        <v>106.1</v>
+      </c>
+      <c r="D25">
+        <v>25704</v>
+      </c>
+      <c r="E25">
+        <v>2005290</v>
+      </c>
+      <c r="F25" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" t="s">
+        <v>91</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>2005290</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26">
+        <v>22075</v>
+      </c>
+      <c r="C26">
+        <v>92.23</v>
+      </c>
+      <c r="D26">
+        <v>40838.75</v>
+      </c>
+      <c r="E26">
+        <v>2035977.25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>90</v>
+      </c>
+      <c r="G26" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>2035977.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>14660</v>
+      </c>
+      <c r="C27">
+        <v>120.16</v>
+      </c>
+      <c r="D27">
+        <v>23456</v>
+      </c>
+      <c r="E27">
+        <v>1761545.6</v>
+      </c>
+      <c r="F27" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1761545.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28">
+        <v>14901</v>
+      </c>
+      <c r="C28">
+        <v>132.26</v>
+      </c>
+      <c r="D28">
+        <v>-15050.01</v>
+      </c>
+      <c r="E28">
+        <v>1970806.26</v>
+      </c>
+      <c r="F28" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1970806.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29">
+        <v>70</v>
+      </c>
+      <c r="C29">
+        <v>23.1</v>
+      </c>
+      <c r="D29">
+        <v>21.7</v>
+      </c>
+      <c r="E29">
+        <v>1617</v>
+      </c>
+      <c r="F29" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30">
+        <v>3000</v>
+      </c>
+      <c r="C30">
+        <v>10.97</v>
+      </c>
+      <c r="D30">
+        <v>235.2</v>
+      </c>
+      <c r="E30">
+        <v>32910</v>
+      </c>
+      <c r="F30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30">
+        <v>0.784</v>
+      </c>
+      <c r="I30">
+        <v>25801.44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31">
+        <v>821</v>
+      </c>
+      <c r="C31">
+        <v>206.15</v>
+      </c>
+      <c r="D31">
+        <v>-8645.129999999999</v>
+      </c>
+      <c r="E31">
+        <v>169249.15</v>
+      </c>
+      <c r="F31" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>169249.15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32">
+        <v>200</v>
+      </c>
+      <c r="C32">
+        <v>6.26</v>
+      </c>
+      <c r="D32">
+        <v>-1.57</v>
+      </c>
+      <c r="E32">
+        <v>1252</v>
+      </c>
+      <c r="F32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32">
+        <v>0.784</v>
+      </c>
+      <c r="I32">
+        <v>981.5700000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>320.42</v>
+      </c>
+      <c r="D33">
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="E33">
+        <v>4806.3</v>
+      </c>
+      <c r="F33" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>4806.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34">
+        <v>659624</v>
+      </c>
+      <c r="C34">
+        <v>31.96</v>
+      </c>
+      <c r="D34">
+        <v>336408.24</v>
+      </c>
+      <c r="E34">
+        <v>21081583.04</v>
+      </c>
+      <c r="F34" t="s">
+        <v>90</v>
+      </c>
+      <c r="G34" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>21081583.04</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35">
+        <v>29</v>
+      </c>
+      <c r="C35">
+        <v>286.82</v>
+      </c>
+      <c r="D35">
+        <v>-100.63</v>
+      </c>
+      <c r="E35">
+        <v>8317.780000000001</v>
+      </c>
+      <c r="F35" t="s">
+        <v>90</v>
+      </c>
+      <c r="G35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>8317.780000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36">
+        <v>103455</v>
+      </c>
+      <c r="C36">
+        <v>53.2261</v>
+      </c>
+      <c r="D36">
+        <v>35805.78</v>
+      </c>
+      <c r="E36">
+        <v>5506506.18</v>
+      </c>
+      <c r="F36" t="s">
+        <v>90</v>
+      </c>
+      <c r="G36" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>5506506.18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37">
+        <v>5</v>
+      </c>
+      <c r="C37">
+        <v>197.75</v>
+      </c>
+      <c r="D37">
+        <v>-26.2</v>
+      </c>
+      <c r="E37">
+        <v>988.75</v>
+      </c>
+      <c r="F37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G37" t="s">
+        <v>91</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>988.75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38">
+        <v>45862</v>
+      </c>
+      <c r="C38">
+        <v>37.99</v>
+      </c>
+      <c r="D38">
+        <v>24765.48</v>
+      </c>
+      <c r="E38">
+        <v>1742297.38</v>
+      </c>
+      <c r="F38" t="s">
+        <v>90</v>
+      </c>
+      <c r="G38" t="s">
+        <v>91</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>1742297.38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39">
+        <v>13</v>
+      </c>
+      <c r="C39">
+        <v>94.3</v>
+      </c>
+      <c r="D39">
+        <v>21.71</v>
+      </c>
+      <c r="E39">
+        <v>1225.9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>90</v>
+      </c>
+      <c r="G39" t="s">
+        <v>91</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>1225.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+      <c r="C40">
+        <v>169.25</v>
+      </c>
+      <c r="D40">
+        <v>23.6</v>
+      </c>
+      <c r="E40">
+        <v>1692.5</v>
+      </c>
+      <c r="F40" t="s">
+        <v>90</v>
+      </c>
+      <c r="G40" t="s">
+        <v>91</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>1692.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41">
+        <v>361</v>
+      </c>
+      <c r="C41">
+        <v>192.64</v>
+      </c>
+      <c r="D41">
+        <v>129.96</v>
+      </c>
+      <c r="E41">
+        <v>69543.03999999999</v>
+      </c>
+      <c r="F41" t="s">
+        <v>90</v>
+      </c>
+      <c r="G41" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>69543.03999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42">
+        <v>800</v>
+      </c>
+      <c r="C42">
+        <v>58.55</v>
+      </c>
+      <c r="D42">
+        <v>-31.36</v>
+      </c>
+      <c r="E42">
+        <v>46840</v>
+      </c>
+      <c r="F42" t="s">
+        <v>89</v>
+      </c>
+      <c r="G42" t="s">
+        <v>91</v>
+      </c>
+      <c r="H42">
+        <v>0.784</v>
+      </c>
+      <c r="I42">
+        <v>36722.56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43">
+        <v>612026</v>
+      </c>
+      <c r="C43">
+        <v>30.74</v>
+      </c>
+      <c r="D43">
+        <v>24481.04</v>
+      </c>
+      <c r="E43">
+        <v>18813679.24</v>
+      </c>
+      <c r="F43" t="s">
+        <v>90</v>
+      </c>
+      <c r="G43" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>18813679.24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44">
+        <v>401</v>
+      </c>
+      <c r="C44">
+        <v>575.79</v>
+      </c>
+      <c r="D44">
+        <v>-1042.6</v>
+      </c>
+      <c r="E44">
+        <v>230891.79</v>
+      </c>
+      <c r="F44" t="s">
+        <v>90</v>
+      </c>
+      <c r="G44" t="s">
+        <v>91</v>
+      </c>
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>230891.79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45">
+        <v>5000</v>
+      </c>
+      <c r="C45">
+        <v>117.01</v>
+      </c>
+      <c r="D45">
+        <v>12650</v>
+      </c>
+      <c r="E45">
+        <v>585050</v>
+      </c>
+      <c r="F45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G45" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>585050</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>102.04</v>
+      </c>
+      <c r="D46">
+        <v>1.34</v>
+      </c>
+      <c r="E46">
+        <v>102.04</v>
+      </c>
+      <c r="F46" t="s">
+        <v>90</v>
+      </c>
+      <c r="G46" t="s">
+        <v>91</v>
+      </c>
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>102.04</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47">
+        <v>36</v>
+      </c>
+      <c r="C47">
+        <v>138.38</v>
+      </c>
+      <c r="D47">
+        <v>105.12</v>
+      </c>
+      <c r="E47">
+        <v>4981.68</v>
+      </c>
+      <c r="F47" t="s">
+        <v>90</v>
+      </c>
+      <c r="G47" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>4981.68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48">
+        <v>17</v>
+      </c>
+      <c r="C48">
+        <v>410.86</v>
+      </c>
+      <c r="D48">
+        <v>-196.86</v>
+      </c>
+      <c r="E48">
+        <v>6984.62</v>
+      </c>
+      <c r="F48" t="s">
+        <v>90</v>
+      </c>
+      <c r="G48" t="s">
+        <v>91</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>6984.62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49">
+        <v>30900</v>
+      </c>
+      <c r="C49">
+        <v>173.47</v>
+      </c>
+      <c r="D49">
+        <v>305292</v>
+      </c>
+      <c r="E49">
+        <v>5360223</v>
+      </c>
+      <c r="F49" t="s">
+        <v>90</v>
+      </c>
+      <c r="G49" t="s">
+        <v>91</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>5360223</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50">
+        <v>76000</v>
+      </c>
+      <c r="C50">
+        <v>39.71</v>
+      </c>
+      <c r="D50">
+        <v>50920</v>
+      </c>
+      <c r="E50">
+        <v>3017960</v>
+      </c>
+      <c r="F50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G50" t="s">
+        <v>91</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>3017960</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51">
+        <v>1662</v>
+      </c>
+      <c r="C51">
+        <v>1095.21</v>
+      </c>
+      <c r="D51">
+        <v>35334.12</v>
+      </c>
+      <c r="E51">
+        <v>1820239.02</v>
+      </c>
+      <c r="F51" t="s">
+        <v>90</v>
+      </c>
+      <c r="G51" t="s">
+        <v>91</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>1820239.02</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52">
+        <v>626620</v>
+      </c>
+      <c r="C52">
+        <v>32.79</v>
+      </c>
+      <c r="D52">
+        <v>62662</v>
+      </c>
+      <c r="E52">
+        <v>20546869.8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>90</v>
+      </c>
+      <c r="G52" t="s">
+        <v>91</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>20546869.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53">
+        <v>42</v>
+      </c>
+      <c r="C53">
+        <v>155.28</v>
+      </c>
+      <c r="D53">
+        <v>-48.72</v>
+      </c>
+      <c r="E53">
+        <v>6521.76</v>
+      </c>
+      <c r="F53" t="s">
+        <v>90</v>
+      </c>
+      <c r="G53" t="s">
+        <v>91</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>6521.76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54">
+        <v>20</v>
+      </c>
+      <c r="C54">
+        <v>309.4</v>
+      </c>
+      <c r="D54">
+        <v>35</v>
+      </c>
+      <c r="E54">
+        <v>6188</v>
+      </c>
+      <c r="F54" t="s">
+        <v>90</v>
+      </c>
+      <c r="G54" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>6188</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55">
+        <v>611583</v>
+      </c>
+      <c r="C55">
+        <v>29.51</v>
+      </c>
+      <c r="D55">
+        <v>30579.15</v>
+      </c>
+      <c r="E55">
+        <v>18047814.33</v>
+      </c>
+      <c r="F55" t="s">
+        <v>90</v>
+      </c>
+      <c r="G55" t="s">
+        <v>91</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>18047814.33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56">
+        <v>3800</v>
+      </c>
+      <c r="C56">
+        <v>731.87</v>
+      </c>
+      <c r="D56">
+        <v>418380</v>
+      </c>
+      <c r="E56">
+        <v>2781106</v>
+      </c>
+      <c r="F56" t="s">
+        <v>90</v>
+      </c>
+      <c r="G56" t="s">
+        <v>91</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <v>2781106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57">
+        <v>1451</v>
+      </c>
+      <c r="C57">
+        <v>69.92</v>
+      </c>
+      <c r="D57">
+        <v>1349.43</v>
+      </c>
+      <c r="E57">
+        <v>101453.92</v>
+      </c>
+      <c r="F57" t="s">
+        <v>90</v>
+      </c>
+      <c r="G57" t="s">
+        <v>91</v>
+      </c>
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>101453.92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58">
+        <v>1794</v>
+      </c>
+      <c r="C58">
+        <v>5.52</v>
+      </c>
+      <c r="D58">
+        <v>-35.88</v>
+      </c>
+      <c r="E58">
+        <v>9902.879999999999</v>
+      </c>
+      <c r="F58" t="s">
+        <v>90</v>
+      </c>
+      <c r="G58" t="s">
+        <v>91</v>
+      </c>
+      <c r="H58">
+        <v>1</v>
+      </c>
+      <c r="I58">
+        <v>9902.879999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>47</v>
+      </c>
+      <c r="B59">
+        <v>3</v>
+      </c>
+      <c r="C59">
+        <v>988.87</v>
+      </c>
+      <c r="D59">
+        <v>62.82</v>
+      </c>
+      <c r="E59">
+        <v>2966.61</v>
+      </c>
+      <c r="F59" t="s">
+        <v>90</v>
+      </c>
+      <c r="G59" t="s">
+        <v>91</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59">
+        <v>2966.61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>48</v>
+      </c>
+      <c r="B60">
+        <v>8000</v>
+      </c>
+      <c r="C60">
+        <v>1.98</v>
+      </c>
+      <c r="D60">
+        <v>125.44</v>
+      </c>
+      <c r="E60">
+        <v>15840</v>
+      </c>
+      <c r="F60" t="s">
+        <v>89</v>
+      </c>
+      <c r="G60" t="s">
+        <v>91</v>
+      </c>
+      <c r="H60">
+        <v>0.784</v>
+      </c>
+      <c r="I60">
+        <v>12418.56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>49</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>1817.31</v>
+      </c>
+      <c r="D61">
+        <v>-233.98</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61" t="s">
+        <v>90</v>
+      </c>
+      <c r="G61" t="s">
+        <v>91</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>50</v>
+      </c>
+      <c r="B62">
+        <v>2747</v>
+      </c>
+      <c r="C62">
+        <v>558.6</v>
+      </c>
+      <c r="D62">
+        <v>-23074.8</v>
+      </c>
+      <c r="E62">
+        <v>1534474.2</v>
+      </c>
+      <c r="F62" t="s">
+        <v>90</v>
+      </c>
+      <c r="G62" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="I62">
+        <v>1534474.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>51</v>
+      </c>
+      <c r="B63">
+        <v>18100</v>
+      </c>
+      <c r="C63">
+        <v>44.87</v>
+      </c>
+      <c r="D63">
+        <v>8688</v>
+      </c>
+      <c r="E63">
+        <v>812147</v>
+      </c>
+      <c r="F63" t="s">
+        <v>90</v>
+      </c>
+      <c r="G63" t="s">
+        <v>91</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>812147</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64">
+        <v>100</v>
+      </c>
+      <c r="C64">
+        <v>63.57</v>
+      </c>
+      <c r="D64">
+        <v>12</v>
+      </c>
+      <c r="E64">
+        <v>6357</v>
+      </c>
+      <c r="F64" t="s">
+        <v>90</v>
+      </c>
+      <c r="G64" t="s">
+        <v>91</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>6357</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>53</v>
+      </c>
+      <c r="B65">
+        <v>34</v>
+      </c>
+      <c r="C65">
+        <v>183.98</v>
+      </c>
+      <c r="D65">
+        <v>-19.72</v>
+      </c>
+      <c r="E65">
+        <v>6255.32</v>
+      </c>
+      <c r="F65" t="s">
+        <v>90</v>
+      </c>
+      <c r="G65" t="s">
+        <v>91</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>6255.32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>54</v>
+      </c>
+      <c r="B66">
+        <v>10</v>
+      </c>
+      <c r="C66">
+        <v>109.0957</v>
+      </c>
+      <c r="D66">
+        <v>20.96</v>
+      </c>
+      <c r="E66">
+        <v>1090.96</v>
+      </c>
+      <c r="F66" t="s">
+        <v>90</v>
+      </c>
+      <c r="G66" t="s">
+        <v>91</v>
+      </c>
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>1090.96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>55</v>
+      </c>
+      <c r="B67">
+        <v>8810</v>
+      </c>
+      <c r="C67">
+        <v>169.46</v>
+      </c>
+      <c r="D67">
+        <v>2378.7</v>
+      </c>
+      <c r="E67">
+        <v>1492942.6</v>
+      </c>
+      <c r="F67" t="s">
+        <v>90</v>
+      </c>
+      <c r="G67" t="s">
+        <v>91</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>1492942.6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68">
+        <v>24680</v>
+      </c>
+      <c r="C68">
+        <v>681.61</v>
+      </c>
+      <c r="D68">
+        <v>215456.4</v>
+      </c>
+      <c r="E68">
+        <v>16822134.8</v>
+      </c>
+      <c r="F68" t="s">
+        <v>90</v>
+      </c>
+      <c r="G68" t="s">
+        <v>91</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68">
+        <v>16822134.8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>57</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>44.04</v>
+      </c>
+      <c r="D69">
+        <v>-1694.31</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69" t="s">
+        <v>90</v>
+      </c>
+      <c r="G69" t="s">
+        <v>91</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70">
+        <v>9000</v>
+      </c>
+      <c r="C70">
+        <v>103.83</v>
+      </c>
+      <c r="D70">
+        <v>15390</v>
+      </c>
+      <c r="E70">
+        <v>934470</v>
+      </c>
+      <c r="F70" t="s">
+        <v>90</v>
+      </c>
+      <c r="G70" t="s">
+        <v>91</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>934470</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71">
+        <v>1820</v>
+      </c>
+      <c r="C71">
+        <v>172.87</v>
+      </c>
+      <c r="D71">
+        <v>-54.6</v>
+      </c>
+      <c r="E71">
+        <v>314623.4</v>
+      </c>
+      <c r="F71" t="s">
+        <v>90</v>
+      </c>
+      <c r="G71" t="s">
+        <v>91</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>314623.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>60</v>
+      </c>
+      <c r="B72">
+        <v>66900</v>
+      </c>
+      <c r="C72">
+        <v>21.17</v>
+      </c>
+      <c r="D72">
+        <v>-9965.299999999999</v>
+      </c>
+      <c r="E72">
+        <v>1416273</v>
+      </c>
+      <c r="F72" t="s">
+        <v>89</v>
+      </c>
+      <c r="G72" t="s">
+        <v>91</v>
+      </c>
+      <c r="H72">
+        <v>0.784</v>
+      </c>
+      <c r="I72">
+        <v>1110358.03</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73">
+        <v>143200</v>
+      </c>
+      <c r="C73">
+        <v>31.69</v>
+      </c>
+      <c r="D73">
+        <v>24344</v>
+      </c>
+      <c r="E73">
+        <v>4538008</v>
+      </c>
+      <c r="F73" t="s">
+        <v>90</v>
+      </c>
+      <c r="G73" t="s">
+        <v>91</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>4538008</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74">
+        <v>10700</v>
+      </c>
+      <c r="C74">
+        <v>100.44</v>
+      </c>
+      <c r="D74">
+        <v>5243</v>
+      </c>
+      <c r="E74">
+        <v>1074708</v>
+      </c>
+      <c r="F74" t="s">
+        <v>90</v>
+      </c>
+      <c r="G74" t="s">
+        <v>91</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>1074708</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75">
+        <v>7000</v>
+      </c>
+      <c r="C75">
+        <v>67.53</v>
+      </c>
+      <c r="D75">
+        <v>-3850</v>
+      </c>
+      <c r="E75">
+        <v>472710</v>
+      </c>
+      <c r="F75" t="s">
+        <v>90</v>
+      </c>
+      <c r="G75" t="s">
+        <v>91</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>472710</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76">
+        <v>20100</v>
+      </c>
+      <c r="C76">
+        <v>3.8</v>
+      </c>
+      <c r="D76">
+        <v>-201</v>
+      </c>
+      <c r="E76">
+        <v>76380</v>
+      </c>
+      <c r="F76" t="s">
+        <v>90</v>
+      </c>
+      <c r="G76" t="s">
+        <v>91</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76">
+        <v>76380</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77">
+        <v>251.45</v>
+      </c>
+      <c r="D77">
+        <v>11.44</v>
+      </c>
+      <c r="E77">
+        <v>502.9</v>
+      </c>
+      <c r="F77" t="s">
+        <v>90</v>
+      </c>
+      <c r="G77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77">
+        <v>502.9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78">
+        <v>51700</v>
+      </c>
+      <c r="C78">
+        <v>36.28</v>
+      </c>
+      <c r="D78">
+        <v>4458.55</v>
+      </c>
+      <c r="E78">
+        <v>1875676</v>
+      </c>
+      <c r="F78" t="s">
+        <v>89</v>
+      </c>
+      <c r="G78" t="s">
+        <v>91</v>
+      </c>
+      <c r="H78">
+        <v>0.784</v>
+      </c>
+      <c r="I78">
+        <v>1470529.98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B79">
+        <v>503600</v>
+      </c>
+      <c r="C79">
+        <v>6.69</v>
+      </c>
+      <c r="D79">
+        <v>3948.17</v>
+      </c>
+      <c r="E79">
+        <v>3369084</v>
+      </c>
+      <c r="F79" t="s">
+        <v>89</v>
+      </c>
+      <c r="G79" t="s">
+        <v>91</v>
+      </c>
+      <c r="H79">
+        <v>0.784</v>
+      </c>
+      <c r="I79">
+        <v>2641361.86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>94.45999999999999</v>
+      </c>
+      <c r="D80">
+        <v>0.1</v>
+      </c>
+      <c r="E80">
+        <v>94.45999999999999</v>
+      </c>
+      <c r="F80" t="s">
+        <v>90</v>
+      </c>
+      <c r="G80" t="s">
+        <v>91</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80">
+        <v>94.45999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>69</v>
+      </c>
+      <c r="B81">
+        <v>1600</v>
+      </c>
+      <c r="C81">
+        <v>169.23</v>
+      </c>
+      <c r="D81">
+        <v>-32</v>
+      </c>
+      <c r="E81">
+        <v>270768</v>
+      </c>
+      <c r="F81" t="s">
+        <v>90</v>
+      </c>
+      <c r="G81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
+        <v>270768</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>70</v>
+      </c>
+      <c r="B82">
+        <v>6000</v>
+      </c>
+      <c r="C82">
+        <v>26.2902</v>
+      </c>
+      <c r="D82">
+        <v>2641.2</v>
+      </c>
+      <c r="E82">
+        <v>157741.2</v>
+      </c>
+      <c r="F82" t="s">
+        <v>90</v>
+      </c>
+      <c r="G82" t="s">
+        <v>91</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>157741.2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>71</v>
+      </c>
+      <c r="B83">
+        <v>21</v>
+      </c>
+      <c r="C83">
+        <v>341.02</v>
+      </c>
+      <c r="D83">
+        <v>211.05</v>
+      </c>
+      <c r="E83">
+        <v>7161.42</v>
+      </c>
+      <c r="F83" t="s">
+        <v>90</v>
+      </c>
+      <c r="G83" t="s">
+        <v>91</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83">
+        <v>7161.42</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" t="s">
+        <v>72</v>
+      </c>
+      <c r="B84">
+        <v>10</v>
+      </c>
+      <c r="C84">
+        <v>160.38</v>
+      </c>
+      <c r="D84">
+        <v>-4.7</v>
+      </c>
+      <c r="E84">
+        <v>1603.8</v>
+      </c>
+      <c r="F84" t="s">
+        <v>90</v>
+      </c>
+      <c r="G84" t="s">
+        <v>91</v>
+      </c>
+      <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84">
+        <v>1603.8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" t="s">
+        <v>73</v>
+      </c>
+      <c r="B85">
+        <v>6003</v>
+      </c>
+      <c r="C85">
+        <v>47.34</v>
+      </c>
+      <c r="D85">
+        <v>-1380.69</v>
+      </c>
+      <c r="E85">
+        <v>284182.02</v>
+      </c>
+      <c r="F85" t="s">
+        <v>90</v>
+      </c>
+      <c r="G85" t="s">
+        <v>91</v>
+      </c>
+      <c r="H85">
+        <v>1</v>
+      </c>
+      <c r="I85">
+        <v>284182.02</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" t="s">
+        <v>74</v>
+      </c>
+      <c r="B86">
+        <v>20000</v>
+      </c>
+      <c r="C86">
+        <v>145.3</v>
+      </c>
+      <c r="D86">
+        <v>11400</v>
+      </c>
+      <c r="E86">
+        <v>2906000</v>
+      </c>
+      <c r="F86" t="s">
+        <v>90</v>
+      </c>
+      <c r="G86" t="s">
+        <v>91</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>2906000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" t="s">
+        <v>75</v>
+      </c>
+      <c r="B87">
+        <v>143300</v>
+      </c>
+      <c r="C87">
+        <v>4.68</v>
+      </c>
+      <c r="D87">
+        <v>1123.46</v>
+      </c>
+      <c r="E87">
+        <v>670644</v>
+      </c>
+      <c r="F87" t="s">
+        <v>89</v>
+      </c>
+      <c r="G87" t="s">
+        <v>91</v>
+      </c>
+      <c r="H87">
+        <v>0.784</v>
+      </c>
+      <c r="I87">
+        <v>525784.9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" t="s">
+        <v>76</v>
+      </c>
+      <c r="B88">
+        <v>271664</v>
+      </c>
+      <c r="C88">
+        <v>20.9</v>
+      </c>
+      <c r="D88">
+        <v>27166.4</v>
+      </c>
+      <c r="E88">
+        <v>5677777.6</v>
+      </c>
+      <c r="F88" t="s">
+        <v>90</v>
+      </c>
+      <c r="G88" t="s">
+        <v>92</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>5677777.6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" t="s">
+        <v>77</v>
+      </c>
+      <c r="B89">
+        <v>224882</v>
+      </c>
+      <c r="C89">
         <v>25.36</v>
       </c>
-      <c r="D2">
-        <v>979.38</v>
-      </c>
-      <c r="E2">
-        <v>275967.52</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>275967.52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3">
-        <v>96120</v>
-      </c>
-      <c r="C3">
+      <c r="D89">
+        <v>20239.38</v>
+      </c>
+      <c r="E89">
+        <v>5703007.52</v>
+      </c>
+      <c r="F89" t="s">
+        <v>90</v>
+      </c>
+      <c r="G89" t="s">
+        <v>92</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89">
+        <v>5703007.52</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" t="s">
+        <v>78</v>
+      </c>
+      <c r="B90">
+        <v>485540</v>
+      </c>
+      <c r="C90">
         <v>100.43</v>
       </c>
-      <c r="D3">
-        <v>961.2</v>
-      </c>
-      <c r="E3">
-        <v>9653331.6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>9653331.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
+      <c r="D90">
+        <v>4855.4</v>
+      </c>
+      <c r="E90">
+        <v>48762782.2</v>
+      </c>
+      <c r="F90" t="s">
+        <v>90</v>
+      </c>
+      <c r="G90" t="s">
+        <v>92</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>48762782.2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" t="s">
+        <v>79</v>
+      </c>
+      <c r="B91">
         <v>1521</v>
       </c>
-      <c r="C4">
+      <c r="C91">
         <v>42.41</v>
       </c>
-      <c r="D4">
+      <c r="D91">
         <v>106.47</v>
       </c>
-      <c r="E4">
+      <c r="E91">
         <v>64505.61</v>
       </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+      <c r="F91" t="s">
+        <v>90</v>
+      </c>
+      <c r="G91" t="s">
+        <v>92</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
         <v>64505.61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" t="s">
+        <v>80</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>109.17</v>
+      </c>
+      <c r="D92">
+        <v>2324.41</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92" t="s">
+        <v>90</v>
+      </c>
+      <c r="G92" t="s">
+        <v>93</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>81</v>
+      </c>
+      <c r="B93">
+        <v>59428</v>
+      </c>
+      <c r="C93">
+        <v>45.39</v>
+      </c>
+      <c r="D93">
+        <v>22582.64</v>
+      </c>
+      <c r="E93">
+        <v>2697436.92</v>
+      </c>
+      <c r="F93" t="s">
+        <v>90</v>
+      </c>
+      <c r="G93" t="s">
+        <v>93</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>2697436.92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>82</v>
+      </c>
+      <c r="B94">
+        <v>6788</v>
+      </c>
+      <c r="C94">
+        <v>54.2</v>
+      </c>
+      <c r="D94">
+        <v>-3869.16</v>
+      </c>
+      <c r="E94">
+        <v>367909.6</v>
+      </c>
+      <c r="F94" t="s">
+        <v>90</v>
+      </c>
+      <c r="G94" t="s">
+        <v>93</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94">
+        <v>367909.6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>83</v>
+      </c>
+      <c r="B95">
+        <v>100</v>
+      </c>
+      <c r="C95">
+        <v>84.25</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>8425</v>
+      </c>
+      <c r="F95" t="s">
+        <v>90</v>
+      </c>
+      <c r="G95" t="s">
+        <v>93</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>8425</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>84</v>
+      </c>
+      <c r="B96">
+        <v>33850</v>
+      </c>
+      <c r="C96">
+        <v>59.45</v>
+      </c>
+      <c r="D96">
+        <v>2031</v>
+      </c>
+      <c r="E96">
+        <v>2012382.5</v>
+      </c>
+      <c r="F96" t="s">
+        <v>90</v>
+      </c>
+      <c r="G96" t="s">
+        <v>93</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
+        <v>2012382.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>85</v>
+      </c>
+      <c r="B97">
+        <v>33</v>
+      </c>
+      <c r="C97">
+        <v>58.19</v>
+      </c>
+      <c r="D97">
+        <v>-8.25</v>
+      </c>
+      <c r="E97">
+        <v>1920.27</v>
+      </c>
+      <c r="F97" t="s">
+        <v>90</v>
+      </c>
+      <c r="G97" t="s">
+        <v>94</v>
+      </c>
+      <c r="H97">
+        <v>1</v>
+      </c>
+      <c r="I97">
+        <v>1920.27</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>86</v>
+      </c>
+      <c r="B98">
+        <v>333</v>
+      </c>
+      <c r="C98">
+        <v>0.89</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>296.37</v>
+      </c>
+      <c r="F98" t="s">
+        <v>89</v>
+      </c>
+      <c r="H98">
+        <v>0.784</v>
+      </c>
+      <c r="I98">
+        <v>232.35</v>
       </c>
     </row>
   </sheetData>
